--- a/artfynd/A 19311-2026 artfynd.xlsx
+++ b/artfynd/A 19311-2026 artfynd.xlsx
@@ -2022,48 +2022,56 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134036440</v>
+        <v>134036557</v>
       </c>
       <c r="B14" t="n">
-        <v>75326</v>
+        <v>57975</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447135</v>
+        <v>447291</v>
       </c>
       <c r="R14" t="n">
-        <v>7023309</v>
+        <v>7023405</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2092,7 +2100,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2102,19 +2110,19 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På bark vid basen av 200-årig gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="b">
         <v>0</v>
@@ -2122,68 +2130,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134036557</v>
+        <v>134036440</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>75326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447291</v>
+        <v>447135</v>
       </c>
       <c r="R15" t="n">
-        <v>7023405</v>
+        <v>7023309</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2222,19 +2222,19 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På bark vid basen av 200-årig gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="b">
         <v>0</v>
@@ -2242,12 +2242,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2366,32 +2366,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134036409</v>
+        <v>134036434</v>
       </c>
       <c r="B17" t="n">
-        <v>79359</v>
+        <v>99519</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2401,13 +2401,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447125</v>
+        <v>447200</v>
       </c>
       <c r="R17" t="n">
-        <v>7023349</v>
+        <v>7023563</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>10 bålar på gammal gran i gammal granskog</t>
+          <t>På marken i äldre granskog vid dike</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2478,32 +2478,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134036434</v>
+        <v>134036409</v>
       </c>
       <c r="B18" t="n">
-        <v>99519</v>
+        <v>79359</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447200</v>
+        <v>447125</v>
       </c>
       <c r="R18" t="n">
-        <v>7023563</v>
+        <v>7023349</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2558,12 +2558,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog vid dike</t>
+          <t>10 bålar på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2702,10 +2702,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134036413</v>
+        <v>134036562</v>
       </c>
       <c r="B20" t="n">
-        <v>79359</v>
+        <v>91960</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2713,21 +2713,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2737,13 +2737,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447150</v>
+        <v>447382</v>
       </c>
       <c r="R20" t="n">
-        <v>7023421</v>
+        <v>7023511</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2783,11 +2783,6 @@
       <c r="AB20" t="inlineStr">
         <is>
           <t>16:59</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2802,22 +2797,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134036562</v>
+        <v>134036413</v>
       </c>
       <c r="B21" t="n">
-        <v>91960</v>
+        <v>79359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,21 +2820,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2849,13 +2844,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447382</v>
+        <v>447150</v>
       </c>
       <c r="R21" t="n">
-        <v>7023511</v>
+        <v>7023421</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2895,6 +2890,11 @@
       <c r="AB21" t="inlineStr">
         <is>
           <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2909,12 +2909,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 19311-2026 artfynd.xlsx
+++ b/artfynd/A 19311-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134036405</v>
       </c>
       <c r="B2" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>134036406</v>
       </c>
       <c r="B3" t="n">
-        <v>80479</v>
+        <v>80486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>134036426</v>
       </c>
       <c r="B4" t="n">
-        <v>102683</v>
+        <v>102690</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>134036559</v>
       </c>
       <c r="B5" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134036435</v>
+        <v>134036563</v>
       </c>
       <c r="B6" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,13 +1166,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447156</v>
+        <v>447311</v>
       </c>
       <c r="R6" t="n">
-        <v>7023501</v>
+        <v>7023544</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,12 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gammal gran i gles gammal granskog</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,22 +1226,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134036417</v>
+        <v>134036435</v>
       </c>
       <c r="B7" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447185</v>
+        <v>447156</v>
       </c>
       <c r="R7" t="n">
-        <v>7023463</v>
+        <v>7023501</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1313,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1323,12 +1318,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar, ca 150-200 år gamla</t>
+          <t>På gammal gran i gles gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,32 +1350,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134036418</v>
+        <v>134036417</v>
       </c>
       <c r="B8" t="n">
-        <v>99098</v>
+        <v>79366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1390,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447199</v>
+        <v>447185</v>
       </c>
       <c r="R8" t="n">
-        <v>7023449</v>
+        <v>7023463</v>
       </c>
       <c r="S8" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1425,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1435,12 +1430,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>I dike i gammal barrblandskog</t>
+          <t>Rikligt på gamla granar, ca 150-200 år gamla</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,32 +1462,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134036563</v>
+        <v>134036418</v>
       </c>
       <c r="B9" t="n">
-        <v>79359</v>
+        <v>99105</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1502,13 +1497,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447311</v>
+        <v>447199</v>
       </c>
       <c r="R9" t="n">
-        <v>7023544</v>
+        <v>7023449</v>
       </c>
       <c r="S9" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1537,7 +1532,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,7 +1542,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I dike i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,12 +1562,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1577,7 +1577,7 @@
         <v>134036403</v>
       </c>
       <c r="B10" t="n">
-        <v>80486</v>
+        <v>80493</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>134036427</v>
       </c>
       <c r="B11" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>134036423</v>
       </c>
       <c r="B12" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>134036399</v>
       </c>
       <c r="B13" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>134036440</v>
       </c>
       <c r="B15" t="n">
-        <v>75326</v>
+        <v>75333</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>134036408</v>
       </c>
       <c r="B16" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>134036434</v>
       </c>
       <c r="B17" t="n">
-        <v>99519</v>
+        <v>99526</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>134036409</v>
       </c>
       <c r="B18" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>134036410</v>
       </c>
       <c r="B19" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>134036562</v>
       </c>
       <c r="B20" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>134036413</v>
       </c>
       <c r="B21" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>134036571</v>
       </c>
       <c r="B22" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134036420</v>
+        <v>134036421</v>
       </c>
       <c r="B23" t="n">
-        <v>96399</v>
+        <v>99526</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3039,21 +3039,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2809</v>
+        <v>219880</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447273</v>
+        <v>447309</v>
       </c>
       <c r="R23" t="n">
-        <v>7023463</v>
+        <v>7023468</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog, höga livsmiljövärden här</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3140,10 +3140,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134036421</v>
+        <v>134036420</v>
       </c>
       <c r="B24" t="n">
-        <v>99519</v>
+        <v>96406</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3151,21 +3151,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219880</v>
+        <v>2809</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3175,10 +3175,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447309</v>
+        <v>447273</v>
       </c>
       <c r="R24" t="n">
-        <v>7023468</v>
+        <v>7023463</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På marken i gammal granskog, höga livsmiljövärden här</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3252,48 +3252,56 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134036568</v>
+        <v>134036564</v>
       </c>
       <c r="B25" t="n">
-        <v>101389</v>
+        <v>57975</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447164</v>
+        <v>447267</v>
       </c>
       <c r="R25" t="n">
-        <v>7023542</v>
+        <v>7023562</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3322,7 +3330,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3332,7 +3340,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3359,56 +3372,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134036564</v>
+        <v>134036568</v>
       </c>
       <c r="B26" t="n">
-        <v>57975</v>
+        <v>101396</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447267</v>
+        <v>447164</v>
       </c>
       <c r="R26" t="n">
-        <v>7023562</v>
+        <v>7023542</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3437,7 +3442,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3447,12 +3452,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3482,7 +3482,7 @@
         <v>134036396</v>
       </c>
       <c r="B27" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>134036439</v>
       </c>
       <c r="B28" t="n">
-        <v>106295</v>
+        <v>106302</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>134036415</v>
       </c>
       <c r="B29" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>134036416</v>
       </c>
       <c r="B31" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>134036438</v>
       </c>
       <c r="B32" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 19311-2026 artfynd.xlsx
+++ b/artfynd/A 19311-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134036405</v>
+        <v>134036426</v>
       </c>
       <c r="B2" t="n">
-        <v>80481</v>
+        <v>102697</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>22</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarptandad daggkåpa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alchemilla oxyodonta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Buser) C. G. Westerl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447082</v>
+        <v>447356</v>
       </c>
       <c r="R2" t="n">
-        <v>7023355</v>
+        <v>7023496</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -745,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +767,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>1 planta på marken i gammal körväg i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +781,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,32 +800,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134036406</v>
+        <v>134036423</v>
       </c>
       <c r="B3" t="n">
-        <v>80486</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447086</v>
+        <v>447330</v>
       </c>
       <c r="R3" t="n">
-        <v>7023355</v>
+        <v>7023486</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +880,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,60 +912,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134036426</v>
+        <v>134036562</v>
       </c>
       <c r="B4" t="n">
-        <v>102690</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>22</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarptandad daggkåpa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alchemilla oxyodonta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Buser) C. G. Westerl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447356</v>
+        <v>447382</v>
       </c>
       <c r="R4" t="n">
-        <v>7023496</v>
+        <v>7023511</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,12 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1 planta på marken i gammal körväg i gammal granskog</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,51 +1001,50 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134036559</v>
+        <v>134036420</v>
       </c>
       <c r="B5" t="n">
-        <v>79366</v>
+        <v>96413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447322</v>
+        <v>447273</v>
       </c>
       <c r="R5" t="n">
-        <v>7023370</v>
+        <v>7023463</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1094,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1099,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog, höga livsmiljövärden här</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,44 +1119,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134036563</v>
+        <v>134036397</v>
       </c>
       <c r="B6" t="n">
-        <v>79366</v>
+        <v>96410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2812</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1166,13 +1166,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447311</v>
+        <v>447125</v>
       </c>
       <c r="R6" t="n">
-        <v>7023544</v>
+        <v>7023295</v>
       </c>
       <c r="S6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1211,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,26 +1231,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134036435</v>
+        <v>134036396</v>
       </c>
       <c r="B7" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1273,13 +1278,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447156</v>
+        <v>447105</v>
       </c>
       <c r="R7" t="n">
-        <v>7023501</v>
+        <v>7023277</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,7 +1313,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1318,12 +1323,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal gran i gles gammal granskog</t>
+          <t>Med apothecier, rikligt på gammal levande gran (över 150 år, 18 cm dbh)</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,14 +1355,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134036417</v>
+        <v>134036399</v>
       </c>
       <c r="B8" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1385,13 +1390,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447185</v>
+        <v>447091</v>
       </c>
       <c r="R8" t="n">
-        <v>7023463</v>
+        <v>7023318</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,7 +1425,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,12 +1435,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar, ca 150-200 år gamla</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,32 +1467,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134036418</v>
+        <v>134036408</v>
       </c>
       <c r="B9" t="n">
-        <v>99105</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1497,13 +1502,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447199</v>
+        <v>447111</v>
       </c>
       <c r="R9" t="n">
-        <v>7023449</v>
+        <v>7023368</v>
       </c>
       <c r="S9" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1532,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1542,12 +1547,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I dike i gammal barrblandskog</t>
+          <t>På gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,32 +1579,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134036403</v>
+        <v>134036409</v>
       </c>
       <c r="B10" t="n">
-        <v>80493</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1609,13 +1614,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447082</v>
+        <v>447125</v>
       </c>
       <c r="R10" t="n">
-        <v>7023346</v>
+        <v>7023349</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1644,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1654,12 +1659,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>10 bålar på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,14 +1691,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134036427</v>
+        <v>134036410</v>
       </c>
       <c r="B11" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1721,13 +1726,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447331</v>
+        <v>447126</v>
       </c>
       <c r="R11" t="n">
-        <v>7023512</v>
+        <v>7023331</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1756,7 +1761,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,12 +1771,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>20 bålar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,32 +1803,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134036423</v>
+        <v>134036413</v>
       </c>
       <c r="B12" t="n">
-        <v>91967</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1833,13 +1838,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447330</v>
+        <v>447150</v>
       </c>
       <c r="R12" t="n">
-        <v>7023486</v>
+        <v>7023421</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1868,7 +1873,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1878,12 +1883,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,14 +1915,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134036399</v>
+        <v>134036415</v>
       </c>
       <c r="B13" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1945,13 +1950,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447091</v>
+        <v>447191</v>
       </c>
       <c r="R13" t="n">
-        <v>7023318</v>
+        <v>7023430</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1980,7 +1985,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1990,12 +1995,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal gran, 175 år, i gammal granskog, längsta bål 40 cm</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,53 +2027,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134036557</v>
+        <v>134036417</v>
       </c>
       <c r="B14" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447291</v>
+        <v>447185</v>
       </c>
       <c r="R14" t="n">
-        <v>7023405</v>
+        <v>7023463</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2100,7 +2097,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2110,19 +2107,19 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Rikligt på gamla granar, ca 150-200 år gamla</t>
         </is>
       </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="b">
         <v>0</v>
@@ -2130,44 +2127,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134036440</v>
+        <v>134036427</v>
       </c>
       <c r="B15" t="n">
-        <v>75333</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2177,13 +2174,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447135</v>
+        <v>447331</v>
       </c>
       <c r="R15" t="n">
-        <v>7023309</v>
+        <v>7023512</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2212,7 +2209,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2222,12 +2219,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På bark vid basen av 200-årig gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2254,14 +2251,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134036408</v>
+        <v>134036435</v>
       </c>
       <c r="B16" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2289,10 +2286,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447111</v>
+        <v>447156</v>
       </c>
       <c r="R16" t="n">
-        <v>7023368</v>
+        <v>7023501</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2324,7 +2321,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2334,12 +2331,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gran i gammal granskog</t>
+          <t>På gammal gran i gles gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,32 +2363,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134036434</v>
+        <v>134036437</v>
       </c>
       <c r="B17" t="n">
-        <v>99526</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2401,13 +2398,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447200</v>
+        <v>447103</v>
       </c>
       <c r="R17" t="n">
-        <v>7023563</v>
+        <v>7023529</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2436,7 +2433,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2446,12 +2443,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog vid dike</t>
+          <t>På 40 cm grov 200-årig tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2478,14 +2475,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134036409</v>
+        <v>134036438</v>
       </c>
       <c r="B18" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2513,13 +2510,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447125</v>
+        <v>447120</v>
       </c>
       <c r="R18" t="n">
-        <v>7023349</v>
+        <v>7023443</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2548,7 +2545,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2558,12 +2555,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>10 bålar på gammal gran i gammal granskog</t>
+          <t>På äldre gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2590,14 +2587,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134036410</v>
+        <v>134036559</v>
       </c>
       <c r="B19" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2625,13 +2622,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447126</v>
+        <v>447322</v>
       </c>
       <c r="R19" t="n">
-        <v>7023331</v>
+        <v>7023370</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2660,7 +2657,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2670,12 +2667,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:51</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>20 bålar på gammal levande gran i gammal granskog</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2690,44 +2682,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134036562</v>
+        <v>134036563</v>
       </c>
       <c r="B20" t="n">
-        <v>91967</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2737,13 +2729,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447382</v>
+        <v>447311</v>
       </c>
       <c r="R20" t="n">
-        <v>7023511</v>
+        <v>7023544</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2772,7 +2764,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2782,7 +2774,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2809,32 +2801,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134036413</v>
+        <v>134036440</v>
       </c>
       <c r="B21" t="n">
-        <v>79366</v>
+        <v>75340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2844,13 +2836,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447150</v>
+        <v>447135</v>
       </c>
       <c r="R21" t="n">
-        <v>7023421</v>
+        <v>7023309</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2879,7 +2871,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2889,12 +2881,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark vid basen av 200-årig gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2921,32 +2913,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134036571</v>
+        <v>134036416</v>
       </c>
       <c r="B22" t="n">
-        <v>99210</v>
+        <v>79992</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2956,10 +2948,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447123</v>
+        <v>447203</v>
       </c>
       <c r="R22" t="n">
-        <v>7023476</v>
+        <v>7023434</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2991,7 +2983,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3001,7 +2993,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På gammal dimensionsavverkningsstubbe av tall i gammal (ca 175 år) barrblandskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3016,44 +3013,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134036421</v>
+        <v>134036405</v>
       </c>
       <c r="B23" t="n">
-        <v>99526</v>
+        <v>80488</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3063,13 +3060,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447309</v>
+        <v>447082</v>
       </c>
       <c r="R23" t="n">
-        <v>7023468</v>
+        <v>7023355</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3098,7 +3095,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3108,12 +3105,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3140,10 +3137,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134036420</v>
+        <v>134036406</v>
       </c>
       <c r="B24" t="n">
-        <v>96406</v>
+        <v>80493</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3151,21 +3148,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2809</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3175,13 +3172,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447273</v>
+        <v>447086</v>
       </c>
       <c r="R24" t="n">
-        <v>7023463</v>
+        <v>7023355</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3210,7 +3207,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3220,12 +3217,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog, höga livsmiljövärden här</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3252,56 +3249,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134036564</v>
+        <v>134036403</v>
       </c>
       <c r="B25" t="n">
-        <v>57975</v>
+        <v>80500</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447267</v>
+        <v>447082</v>
       </c>
       <c r="R25" t="n">
-        <v>7023562</v>
+        <v>7023346</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3330,7 +3319,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3340,12 +3329,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3360,60 +3349,68 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134036568</v>
+        <v>134036556</v>
       </c>
       <c r="B26" t="n">
-        <v>101396</v>
+        <v>57975</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447164</v>
+        <v>447194</v>
       </c>
       <c r="R26" t="n">
-        <v>7023542</v>
+        <v>7023412</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3442,7 +3439,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3452,14 +3449,19 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG26" t="b">
         <v>0</v>
@@ -3479,10 +3481,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134036396</v>
+        <v>134036557</v>
       </c>
       <c r="B27" t="n">
-        <v>79366</v>
+        <v>57975</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3490,37 +3492,45 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447105</v>
+        <v>447291</v>
       </c>
       <c r="R27" t="n">
-        <v>7023277</v>
+        <v>7023405</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3549,7 +3559,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3559,19 +3569,19 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Med apothecier, rikligt på gammal levande gran (över 150 år, 18 cm dbh)</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG27" t="b">
         <v>0</v>
@@ -3579,60 +3589,68 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134036439</v>
+        <v>134036564</v>
       </c>
       <c r="B28" t="n">
-        <v>106302</v>
+        <v>57975</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447089</v>
+        <v>447267</v>
       </c>
       <c r="R28" t="n">
-        <v>7023400</v>
+        <v>7023562</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3661,7 +3679,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3671,12 +3689,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3691,44 +3709,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134036415</v>
+        <v>134036418</v>
       </c>
       <c r="B29" t="n">
-        <v>79366</v>
+        <v>99112</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3738,13 +3756,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447191</v>
+        <v>447199</v>
       </c>
       <c r="R29" t="n">
-        <v>7023430</v>
+        <v>7023449</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3773,7 +3791,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3783,12 +3801,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal gran, 175 år, i gammal granskog, längsta bål 40 cm</t>
+          <t>I dike i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3815,53 +3833,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134036556</v>
+        <v>134036421</v>
       </c>
       <c r="B30" t="n">
-        <v>57975</v>
+        <v>99533</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Åslägden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447194</v>
+        <v>447309</v>
       </c>
       <c r="R30" t="n">
-        <v>7023412</v>
+        <v>7023468</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3893,7 +3903,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3903,19 +3913,19 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="b">
         <v>0</v>
@@ -3923,44 +3933,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134036416</v>
+        <v>134036434</v>
       </c>
       <c r="B31" t="n">
-        <v>79985</v>
+        <v>99533</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>219880</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3970,13 +3980,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447203</v>
+        <v>447200</v>
       </c>
       <c r="R31" t="n">
-        <v>7023434</v>
+        <v>7023563</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4005,7 +4015,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4015,12 +4025,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gammal dimensionsavverkningsstubbe av tall i gammal (ca 175 år) barrblandskog</t>
+          <t>På marken i äldre granskog vid dike</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4047,32 +4057,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134036438</v>
+        <v>134036411</v>
       </c>
       <c r="B32" t="n">
-        <v>79366</v>
+        <v>108274</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220102</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4082,13 +4092,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447120</v>
+        <v>447141</v>
       </c>
       <c r="R32" t="n">
-        <v>7023443</v>
+        <v>7023321</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4117,7 +4127,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4127,12 +4137,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På äldre gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4156,6 +4166,663 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134036439</v>
+      </c>
+      <c r="B33" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Åslägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>447089</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7023400</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134036571</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Åslägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>447123</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7023476</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134036568</v>
+      </c>
+      <c r="B35" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Åslägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>447164</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7023542</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134036422</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99472</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Åslägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>447309</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7023468</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På marken i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134036430</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Åslägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>447248</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7023524</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På marken nära dike i äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134036567</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Åslägden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>447170</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7023542</v>
+      </c>
+      <c r="S38" t="n">
+        <v>9</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
